--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="87">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,10 +120,13 @@
     <t>Door to Groin &lt;= 120 Minutes</t>
   </si>
   <si>
+    <t>D2D</t>
+  </si>
+  <si>
+    <t>Door to Door</t>
+  </si>
+  <si>
     <t>Door2Door</t>
-  </si>
-  <si>
-    <t>Door to Door</t>
   </si>
   <si>
     <t>Door2Discharge</t>
@@ -534,7 +537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -586,188 +589,188 @@
         <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>55</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>83</v>
@@ -778,7 +781,15 @@
         <v>84</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
         <v>85</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
